--- a/config/union/union_level.xlsx
+++ b/config/union/union_level.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="union_level" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="union_level" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1547,12 +1547,9 @@
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>ギルドボスを解放</t>
+          <t>解放公会boss</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1570,8 +1567,6 @@
           <t>길드 던전 개방</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(31到達)</t>
+          <t>成员上限：+1（达到31级）</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1681,7 +1676,7 @@
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>寄付センターを解放</t>
+          <t>开放捐赠中心</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1699,8 +1694,6 @@
           <t>기부 센터 개방</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1790,7 +1783,7 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(32到達)</t>
+          <t>成员上限：+1（达到32级）</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1810,7 +1803,7 @@
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>修行センター、ギルド戦を解放</t>
+          <t>修行中心，解放公会战</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1828,8 +1821,6 @@
           <t>수련 센터 개방, 길드전 개방</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1919,7 +1910,7 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(33到達)</t>
+          <t>成员上限：+1（达到33级）</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1952,8 +1943,6 @@
           <t>404</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2038,7 +2027,7 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(34到達)</t>
+          <t>成员上限：+1（达到34级）</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2057,11 +2046,6 @@
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2099,7 +2083,6 @@
           <t>17500</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>1.02</t>
@@ -2147,7 +2130,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(35到達)</t>
+          <t>成员上限：+1（达到35级）</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2166,11 +2149,6 @@
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2208,7 +2186,6 @@
           <t>18000</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>1.03</t>
@@ -2256,7 +2233,7 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(36到達)</t>
+          <t>成员上限：+1（达到36级）</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2275,11 +2252,6 @@
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2317,7 +2289,6 @@
           <t>18500</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>1.03</t>
@@ -2365,7 +2336,7 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(37到達)</t>
+          <t>成员上限：+1（达到37级）</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2384,11 +2355,6 @@
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2426,7 +2392,6 @@
           <t>19000</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -2474,7 +2439,7 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(38到達)</t>
+          <t>成员上限：+1（达到38级）</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2493,11 +2458,6 @@
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2535,7 +2495,6 @@
           <t>19500</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>1.04</t>
@@ -2583,7 +2542,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(39到達)</t>
+          <t>成员上限：+1（达到39级）</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2603,7 +2562,7 @@
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>副会長を+1人設定可能</t>
+          <t>副会长可设+1人</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2621,8 +2580,6 @@
           <t>설정 가능 부회장 수 +1</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2660,7 +2617,6 @@
           <t>20000</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>1.05</t>
@@ -2708,7 +2664,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(40到達)</t>
+          <t>成员上限：+1（达到40级）</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2727,11 +2683,6 @@
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2769,7 +2720,6 @@
           <t>20500</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>1.05</t>
@@ -2817,7 +2767,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(41到達)</t>
+          <t>成员上限：+1（达到41级）</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2836,11 +2786,6 @@
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2878,7 +2823,6 @@
           <t>21000</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>1.06</t>
@@ -2926,7 +2870,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(42到達)</t>
+          <t>成员上限：+1（达到42级）</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2945,11 +2889,6 @@
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2987,7 +2926,6 @@
           <t>21500</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>1.06</t>
@@ -3035,7 +2973,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(43到達)</t>
+          <t>成员上限：+1（达到43级）</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -3054,11 +2992,6 @@
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3096,7 +3029,6 @@
           <t>22000</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -3144,7 +3076,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(44到達)</t>
+          <t>成员上限：+1（达到44级）</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -3163,11 +3095,6 @@
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3205,7 +3132,6 @@
           <t>22500</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>1.07</t>
@@ -3253,7 +3179,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(45到達)</t>
+          <t>成员上限：+1（达到45级）</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3272,11 +3198,6 @@
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3314,7 +3235,6 @@
           <t>23000</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>1.08</t>
@@ -3362,7 +3282,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(46到達)</t>
+          <t>成员上限：+1（达到46级）</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3381,11 +3301,6 @@
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3423,7 +3338,6 @@
           <t>23500</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>1.08</t>
@@ -3471,7 +3385,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(47到達)</t>
+          <t>成员上限：+1（达到47级）</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3490,11 +3404,6 @@
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3532,7 +3441,6 @@
           <t>24000</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>1.09</t>
@@ -3580,7 +3488,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(48到達)</t>
+          <t>成员上限：+1（达到48级）</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3599,11 +3507,6 @@
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3641,7 +3544,6 @@
           <t>24500</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>1.09</t>
@@ -3689,7 +3591,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>メンバー上限:+1(49到達)</t>
+          <t>成员上限：+1（达到49级）</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3708,11 +3610,6 @@
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
